--- a/report_thermo/熱電対の検定実験_データとグラフ.xlsx
+++ b/report_thermo/熱電対の検定実験_データとグラフ.xlsx
@@ -178,8 +178,10 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
   <style val="1"/>
   <chart>
+    <autoTitleDeleted val="1"/>
     <plotArea>
       <scatterChart>
         <ser>
@@ -319,6 +321,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="in"/>
         <minorTickMark val="none"/>
@@ -358,6 +361,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <numFmt formatCode="0.0" sourceLinked="0"/>
         <majorTickMark val="in"/>
@@ -368,6 +372,7 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -378,13 +383,28 @@
       <a:prstDash val="solid"/>
     </a:ln>
   </spPr>
+  <txPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="900">
+          <a:latin typeface="Times New Roman"/>
+          <a:ea typeface="ＭＳ 明朝"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </txPr>
 </chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
   <style val="1"/>
   <chart>
+    <autoTitleDeleted val="1"/>
     <plotArea>
       <scatterChart>
         <ser>
@@ -524,6 +544,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="in"/>
         <minorTickMark val="none"/>
@@ -563,6 +584,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <numFmt formatCode="0.0" sourceLinked="0"/>
         <majorTickMark val="in"/>
@@ -573,6 +595,7 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -583,13 +606,28 @@
       <a:prstDash val="solid"/>
     </a:ln>
   </spPr>
+  <txPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="900">
+          <a:latin typeface="Times New Roman"/>
+          <a:ea typeface="ＭＳ 明朝"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </txPr>
 </chartSpace>
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
   <style val="1"/>
   <chart>
+    <autoTitleDeleted val="1"/>
     <plotArea>
       <scatterChart>
         <ser>
@@ -729,6 +767,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="in"/>
         <minorTickMark val="none"/>
@@ -768,6 +807,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <numFmt formatCode="0.0" sourceLinked="0"/>
         <majorTickMark val="in"/>
@@ -778,6 +818,7 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -788,13 +829,28 @@
       <a:prstDash val="solid"/>
     </a:ln>
   </spPr>
+  <txPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="900">
+          <a:latin typeface="Times New Roman"/>
+          <a:ea typeface="ＭＳ 明朝"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </txPr>
 </chartSpace>
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
   <style val="1"/>
   <chart>
+    <autoTitleDeleted val="1"/>
     <plotArea>
       <scatterChart>
         <ser>
@@ -927,6 +983,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="in"/>
@@ -967,6 +1024,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="in"/>
@@ -977,6 +1035,7 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -987,13 +1046,28 @@
       <a:prstDash val="solid"/>
     </a:ln>
   </spPr>
+  <txPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="900">
+          <a:latin typeface="Times New Roman"/>
+          <a:ea typeface="ＭＳ 明朝"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </txPr>
 </chartSpace>
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
   <style val="1"/>
   <chart>
+    <autoTitleDeleted val="1"/>
     <plotArea>
       <scatterChart>
         <ser>
@@ -1126,6 +1200,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="in"/>
@@ -1167,6 +1242,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="in"/>
@@ -1177,6 +1253,7 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1187,6 +1264,19 @@
       <a:prstDash val="solid"/>
     </a:ln>
   </spPr>
+  <txPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="900">
+          <a:latin typeface="Times New Roman"/>
+          <a:ea typeface="ＭＳ 明朝"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </txPr>
 </chartSpace>
 </file>
 

--- a/report_thermo/熱電対の検定実験_データとグラフ.xlsx
+++ b/report_thermo/熱電対の検定実験_データとグラフ.xlsx
@@ -179,7 +179,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <roundedCorners val="0"/>
-  <style val="1"/>
+  <style val="2"/>
   <chart>
     <autoTitleDeleted val="1"/>
     <plotArea>
@@ -191,23 +191,23 @@
             <v>測定値</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575">
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="4472C4"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="3"/>
+            <size val="5"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="FFFFFF"/>
+                <a:srgbClr val="4472C4"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="4472C4"/>
                 </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -237,15 +237,15 @@
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="square"/>
+            <symbol val="circle"/>
             <size val="5"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="ED7D31"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="ED7D31"/>
                 </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -269,9 +269,9 @@
             <v>平均値 9.252 mV</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="A5A5A5"/>
               </a:solidFill>
               <a:prstDash val="dash"/>
             </a:ln>
@@ -307,6 +307,16 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="D9D9D9"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <title>
           <tx>
             <rich>
@@ -323,8 +333,17 @@
           </tx>
           <overlay val="0"/>
         </title>
-        <majorTickMark val="in"/>
+        <numFmt formatCode="General" sourceLinked="0"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="D9D9D9"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="20"/>
         <majorUnit val="200"/>
       </valAx>
@@ -339,7 +358,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="D9D9D9"/>
               </a:solidFill>
@@ -363,9 +382,17 @@
           </tx>
           <overlay val="0"/>
         </title>
-        <numFmt formatCode="0.0" sourceLinked="0"/>
-        <majorTickMark val="in"/>
+        <numFmt formatCode="General" sourceLinked="0"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="D9D9D9"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="10"/>
         <majorUnit val="1"/>
       </valAx>
@@ -389,8 +416,11 @@
     <a:p>
       <a:pPr>
         <a:defRPr sz="900">
-          <a:latin typeface="Times New Roman"/>
-          <a:ea typeface="ＭＳ 明朝"/>
+          <a:solidFill>
+            <a:srgbClr val="595959"/>
+          </a:solidFill>
+          <a:latin typeface="游ゴシック"/>
+          <a:ea typeface="游ゴシック"/>
         </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="ja-JP"/>
@@ -402,7 +432,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <roundedCorners val="0"/>
-  <style val="1"/>
+  <style val="2"/>
   <chart>
     <autoTitleDeleted val="1"/>
     <plotArea>
@@ -414,23 +444,23 @@
             <v>測定値</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575">
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="4472C4"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="3"/>
+            <size val="5"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="FFFFFF"/>
+                <a:srgbClr val="4472C4"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="4472C4"/>
                 </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -460,15 +490,15 @@
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="square"/>
+            <symbol val="circle"/>
             <size val="5"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="ED7D31"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="ED7D31"/>
                 </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -492,9 +522,9 @@
             <v>平均値 13.136 mV</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="A5A5A5"/>
               </a:solidFill>
               <a:prstDash val="dash"/>
             </a:ln>
@@ -530,6 +560,16 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="D9D9D9"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <title>
           <tx>
             <rich>
@@ -546,8 +586,17 @@
           </tx>
           <overlay val="0"/>
         </title>
-        <majorTickMark val="in"/>
+        <numFmt formatCode="General" sourceLinked="0"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="D9D9D9"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="20"/>
         <majorUnit val="100"/>
       </valAx>
@@ -562,7 +611,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="D9D9D9"/>
               </a:solidFill>
@@ -586,9 +635,17 @@
           </tx>
           <overlay val="0"/>
         </title>
-        <numFmt formatCode="0.0" sourceLinked="0"/>
-        <majorTickMark val="in"/>
+        <numFmt formatCode="General" sourceLinked="0"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="D9D9D9"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="10"/>
         <majorUnit val="1"/>
       </valAx>
@@ -612,8 +669,11 @@
     <a:p>
       <a:pPr>
         <a:defRPr sz="900">
-          <a:latin typeface="Times New Roman"/>
-          <a:ea typeface="ＭＳ 明朝"/>
+          <a:solidFill>
+            <a:srgbClr val="595959"/>
+          </a:solidFill>
+          <a:latin typeface="游ゴシック"/>
+          <a:ea typeface="游ゴシック"/>
         </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="ja-JP"/>
@@ -625,7 +685,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <roundedCorners val="0"/>
-  <style val="1"/>
+  <style val="2"/>
   <chart>
     <autoTitleDeleted val="1"/>
     <plotArea>
@@ -637,23 +697,23 @@
             <v>測定値</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575">
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="4472C4"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="3"/>
+            <size val="5"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="FFFFFF"/>
+                <a:srgbClr val="4472C4"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="4472C4"/>
                 </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -683,15 +743,15 @@
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="square"/>
+            <symbol val="circle"/>
             <size val="5"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="ED7D31"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="ED7D31"/>
                 </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -715,9 +775,9 @@
             <v>平均値 16.995 mV</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="A5A5A5"/>
               </a:solidFill>
               <a:prstDash val="dash"/>
             </a:ln>
@@ -753,6 +813,16 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="D9D9D9"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <title>
           <tx>
             <rich>
@@ -769,8 +839,17 @@
           </tx>
           <overlay val="0"/>
         </title>
-        <majorTickMark val="in"/>
+        <numFmt formatCode="General" sourceLinked="0"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="D9D9D9"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="20"/>
         <majorUnit val="100"/>
       </valAx>
@@ -785,7 +864,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="D9D9D9"/>
               </a:solidFill>
@@ -809,9 +888,17 @@
           </tx>
           <overlay val="0"/>
         </title>
-        <numFmt formatCode="0.0" sourceLinked="0"/>
-        <majorTickMark val="in"/>
+        <numFmt formatCode="General" sourceLinked="0"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="D9D9D9"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="10"/>
         <majorUnit val="1"/>
       </valAx>
@@ -835,8 +922,11 @@
     <a:p>
       <a:pPr>
         <a:defRPr sz="900">
-          <a:latin typeface="Times New Roman"/>
-          <a:ea typeface="ＭＳ 明朝"/>
+          <a:solidFill>
+            <a:srgbClr val="595959"/>
+          </a:solidFill>
+          <a:latin typeface="游ゴシック"/>
+          <a:ea typeface="游ゴシック"/>
         </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="ja-JP"/>
@@ -848,7 +938,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <roundedCorners val="0"/>
-  <style val="1"/>
+  <style val="2"/>
   <chart>
     <autoTitleDeleted val="1"/>
     <plotArea>
@@ -860,9 +950,9 @@
             <v>近似直線（1次式）</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575">
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="ED7D31"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -893,9 +983,9 @@
             <v>近似曲線（2次式）</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575">
               <a:solidFill>
-                <a:srgbClr val="595959"/>
+                <a:srgbClr val="A5A5A5"/>
               </a:solidFill>
               <a:prstDash val="dash"/>
             </a:ln>
@@ -936,11 +1026,11 @@
             <size val="7"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="4472C4"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="4472C4"/>
                 </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -969,6 +1059,16 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="D9D9D9"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <title>
           <tx>
             <rich>
@@ -985,9 +1085,17 @@
           </tx>
           <overlay val="0"/>
         </title>
-        <numFmt formatCode="0" sourceLinked="0"/>
-        <majorTickMark val="in"/>
+        <numFmt formatCode="General" sourceLinked="0"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="D9D9D9"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="20"/>
         <majorUnit val="50"/>
       </valAx>
@@ -1002,7 +1110,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="D9D9D9"/>
               </a:solidFill>
@@ -1026,9 +1134,17 @@
           </tx>
           <overlay val="0"/>
         </title>
-        <numFmt formatCode="0" sourceLinked="0"/>
-        <majorTickMark val="in"/>
+        <numFmt formatCode="General" sourceLinked="0"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="D9D9D9"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="10"/>
         <majorUnit val="2"/>
       </valAx>
@@ -1052,8 +1168,11 @@
     <a:p>
       <a:pPr>
         <a:defRPr sz="900">
-          <a:latin typeface="Times New Roman"/>
-          <a:ea typeface="ＭＳ 明朝"/>
+          <a:solidFill>
+            <a:srgbClr val="595959"/>
+          </a:solidFill>
+          <a:latin typeface="游ゴシック"/>
+          <a:ea typeface="游ゴシック"/>
         </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="ja-JP"/>
@@ -1065,7 +1184,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <roundedCorners val="0"/>
-  <style val="1"/>
+  <style val="2"/>
   <chart>
     <autoTitleDeleted val="1"/>
     <plotArea>
@@ -1077,9 +1196,9 @@
             <v>近似直線（1次式）</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575">
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="ED7D31"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1110,9 +1229,9 @@
             <v>近似曲線（2次式）</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575">
               <a:solidFill>
-                <a:srgbClr val="595959"/>
+                <a:srgbClr val="A5A5A5"/>
               </a:solidFill>
               <a:prstDash val="dash"/>
             </a:ln>
@@ -1153,11 +1272,11 @@
             <size val="7"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="4472C4"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="4472C4"/>
                 </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1186,6 +1305,16 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="D9D9D9"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <title>
           <tx>
             <rich>
@@ -1202,9 +1331,17 @@
           </tx>
           <overlay val="0"/>
         </title>
-        <numFmt formatCode="0" sourceLinked="0"/>
-        <majorTickMark val="in"/>
+        <numFmt formatCode="General" sourceLinked="0"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="D9D9D9"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="20"/>
         <crosses val="min"/>
         <majorUnit val="50"/>
@@ -1220,7 +1357,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="D9D9D9"/>
               </a:solidFill>
@@ -1244,9 +1381,17 @@
           </tx>
           <overlay val="0"/>
         </title>
-        <numFmt formatCode="0" sourceLinked="0"/>
-        <majorTickMark val="in"/>
+        <numFmt formatCode="General" sourceLinked="0"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="D9D9D9"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="10"/>
         <majorUnit val="1"/>
       </valAx>
@@ -1270,8 +1415,11 @@
     <a:p>
       <a:pPr>
         <a:defRPr sz="900">
-          <a:latin typeface="Times New Roman"/>
-          <a:ea typeface="ＭＳ 明朝"/>
+          <a:solidFill>
+            <a:srgbClr val="595959"/>
+          </a:solidFill>
+          <a:latin typeface="游ゴシック"/>
+          <a:ea typeface="游ゴシック"/>
         </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="ja-JP"/>
